--- a/data/Study_dates_MeLiDos_THUAS.xlsx
+++ b/data/Study_dates_MeLiDos_THUAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/MeLiDos/WP2.2.5_Data_Analysis/AertsEtAl_Dataset_2025/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F9A660E-B1DA-964A-95B3-048EB7DA32D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B73D408-1031-F94A-BFD4-0F33BF2D3F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="1240" windowWidth="30680" windowHeight="21100" xr2:uid="{6A8EC438-0EAD-4B8C-B6CD-E3F36F63E255}"/>
+    <workbookView xWindow="56280" yWindow="2960" windowWidth="30680" windowHeight="21100" xr2:uid="{6A8EC438-0EAD-4B8C-B6CD-E3F36F63E255}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -689,7 +689,7 @@
         <v>45709.586805555555</v>
       </c>
       <c r="F2" s="7">
-        <v>45709.569444444445</v>
+        <v>45712</v>
       </c>
       <c r="G2" s="7">
         <v>45719.421527777777</v>
@@ -716,7 +716,7 @@
         <v>45709.586805555555</v>
       </c>
       <c r="F3" s="7">
-        <v>45709.569444444445</v>
+        <v>45712</v>
       </c>
       <c r="G3" s="7">
         <v>45719.421527777777</v>
@@ -743,7 +743,7 @@
         <v>45709.586805555555</v>
       </c>
       <c r="F4" s="7">
-        <v>45709.569444444445</v>
+        <v>45712</v>
       </c>
       <c r="G4" s="7">
         <v>45719.421527777777</v>

--- a/data/Study_dates_MeLiDos_THUAS.xlsx
+++ b/data/Study_dates_MeLiDos_THUAS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/MeLiDos/WP2.2.5_Data_Analysis/AertsEtAl_Dataset_2025/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B73D408-1031-F94A-BFD4-0F33BF2D3F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0286B919-D82C-544B-A924-EF485EC118F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="56280" yWindow="2960" windowWidth="30680" windowHeight="21100" xr2:uid="{6A8EC438-0EAD-4B8C-B6CD-E3F36F63E255}"/>
   </bookViews>
@@ -1591,7 +1591,7 @@
         <v>45908</v>
       </c>
       <c r="E35" s="7">
-        <v>45845.677083333336</v>
+        <v>45908.677083333336</v>
       </c>
       <c r="F35" s="7">
         <v>45908.681250000001</v>
@@ -1618,7 +1618,7 @@
         <v>45908</v>
       </c>
       <c r="E36" s="7">
-        <v>45845.677083333336</v>
+        <v>45908.677083333336</v>
       </c>
       <c r="F36" s="7">
         <v>45908.681250000001</v>
@@ -1645,7 +1645,7 @@
         <v>45908</v>
       </c>
       <c r="E37" s="7">
-        <v>45845.677083333336</v>
+        <v>45908.677083333336</v>
       </c>
       <c r="F37" s="7">
         <v>45908.681250000001</v>
